--- a/EconAutomation/ea_outputs/private_claimant_directories/G/Gaston, Casper (J. D’Attorney)/GastonC - Case Variables.xlsx
+++ b/EconAutomation/ea_outputs/private_claimant_directories/G/Gaston, Casper (J. D’Attorney)/GastonC - Case Variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericmacbook/Documents/GitHub/EconAutomation-REP/EconAutomation/ea_outputs/private_claimant_directories/G/Gaston, Casper (J. D’Attorney)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EricBussey\GitHub\EconAutomation-REP\EconAutomation\ea_outputs\private_claimant_directories\G\Gaston, Casper (J. D’Attorney)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2E25F6A6D274746F6372C4B5587D1EFB30812E83" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7F62FE-2A31-42E9-887E-2CCF8C88202B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="32000" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-14085" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT_OUTPUTS" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="123">
   <si>
     <t>CASE VARIABLES</t>
   </si>
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>claimant_geozip</t>
-  </si>
-  <si>
-    <t>80439</t>
   </si>
   <si>
     <t>claimant_phone</t>
@@ -1288,7 +1285,7 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:M230"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.83203125" style="1" customWidth="1"/>
@@ -1302,21 +1299,21 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="64"/>
       <c r="C1" s="37"/>
     </row>
-    <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="59"/>
       <c r="C2" s="29"/>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
         <v>2</v>
       </c>
@@ -1325,7 +1322,7 @@
       </c>
       <c r="C3" s="30"/>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
         <v>4</v>
       </c>
@@ -1334,7 +1331,7 @@
       </c>
       <c r="C4" s="20"/>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
         <v>6</v>
       </c>
@@ -1343,7 +1340,7 @@
       </c>
       <c r="C5" s="20"/>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
         <v>8</v>
       </c>
@@ -1352,14 +1349,14 @@
       </c>
       <c r="C6" s="20"/>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="10"/>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
         <v>11</v>
       </c>
@@ -1368,7 +1365,7 @@
       </c>
       <c r="C8" s="10"/>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
         <v>13</v>
       </c>
@@ -1377,7 +1374,7 @@
       </c>
       <c r="C9" s="10"/>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
         <v>15</v>
       </c>
@@ -1386,7 +1383,7 @@
       </c>
       <c r="C10" s="15"/>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
         <v>17</v>
       </c>
@@ -1395,7 +1392,7 @@
       </c>
       <c r="C11" s="15"/>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
         <v>19</v>
       </c>
@@ -1404,7 +1401,7 @@
       </c>
       <c r="C12" s="15"/>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
         <v>21</v>
       </c>
@@ -1413,7 +1410,7 @@
       </c>
       <c r="C13" s="15"/>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
@@ -1422,7 +1419,7 @@
       </c>
       <c r="C14" s="15"/>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
         <v>25</v>
       </c>
@@ -1431,7 +1428,7 @@
       </c>
       <c r="C15" s="15"/>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
         <v>27</v>
       </c>
@@ -1440,7 +1437,7 @@
       </c>
       <c r="C16" s="15"/>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="35" t="s">
         <v>29</v>
       </c>
@@ -1449,7 +1446,7 @@
       </c>
       <c r="C17" s="15"/>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
         <v>31</v>
       </c>
@@ -1458,7 +1455,7 @@
       </c>
       <c r="C18" s="15"/>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="35" t="s">
         <v>33</v>
       </c>
@@ -1467,589 +1464,589 @@
       </c>
       <c r="C19" s="15"/>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="43">
+        <v>70002</v>
+      </c>
+      <c r="C20" s="15"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="15"/>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="35" t="s">
+      <c r="B21" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="C21" s="24"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="24"/>
-    </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="36" t="s">
+      <c r="B22" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="C22" s="24"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="24"/>
-    </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="35" t="s">
+      <c r="B23" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="42" t="s">
+      <c r="C23" s="24"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="24"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="36" t="s">
+      <c r="B24" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="C24" s="24"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="24"/>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="35" t="s">
+      <c r="B25" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="42" t="s">
+      <c r="C25" s="24"/>
+    </row>
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="24"/>
-    </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="36" t="s">
+      <c r="B26" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="C26" s="24"/>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35" t="s">
         <v>48</v>
-      </c>
-      <c r="C26" s="24"/>
-    </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="35" t="s">
-        <v>49</v>
       </c>
       <c r="B27" s="42"/>
       <c r="C27" s="24"/>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B28" s="43"/>
       <c r="C28" s="24"/>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="36" t="s">
-        <v>53</v>
       </c>
       <c r="B30" s="43"/>
       <c r="C30" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" s="43"/>
       <c r="C32" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B33" s="42"/>
       <c r="C33" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B34" s="45"/>
       <c r="C34" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B36" s="46"/>
       <c r="C36" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="46"/>
       <c r="C38" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="36"/>
       <c r="B40" s="46"/>
       <c r="C40" s="12"/>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="47"/>
       <c r="B41" s="48"/>
       <c r="C41" s="12"/>
     </row>
-    <row r="42" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B42" s="61"/>
       <c r="C42" s="31"/>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="34" t="s">
+    </row>
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="46" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="46" t="s">
+      <c r="B44" s="46"/>
+    </row>
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="B44" s="46"/>
-    </row>
-    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="34" t="s">
+      <c r="B45" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="34" t="s">
+    </row>
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="46" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="46" t="s">
+      <c r="B46" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="B46" s="46" t="s">
+    </row>
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="48" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="48" t="s">
+      <c r="B47" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="48" t="s">
+    </row>
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="46" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="46" t="s">
+      <c r="B48" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="46" t="s">
+    </row>
+    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="48" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="48" t="s">
+      <c r="B49" s="48"/>
+    </row>
+    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="48"/>
-    </row>
-    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="46" t="s">
+      <c r="B50" s="46"/>
+    </row>
+    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="48" t="s">
         <v>76</v>
-      </c>
-      <c r="B50" s="46"/>
-    </row>
-    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="48" t="s">
-        <v>77</v>
       </c>
       <c r="B51" s="48"/>
       <c r="C51" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B52" s="46"/>
       <c r="C52" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B53" s="48"/>
       <c r="C53" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B54" s="46"/>
       <c r="C54" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B55" s="48"/>
       <c r="C55" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="46" t="s">
+    </row>
+    <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="48" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="48" t="s">
+      <c r="B57" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="48" t="s">
+    </row>
+    <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="46" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="46" t="s">
+      <c r="B58" s="46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B58" s="46" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="48" t="s">
-        <v>87</v>
-      </c>
       <c r="B59" s="48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="46"/>
       <c r="B60" s="46"/>
     </row>
-    <row r="61" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B61" s="61"/>
       <c r="C61" s="32"/>
     </row>
-    <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="34" t="s">
+    </row>
+    <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="46" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="46" t="s">
+      <c r="B63" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B63" s="46" t="s">
+    </row>
+    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="34" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="34" t="s">
+      <c r="B64" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="B64" s="34" t="s">
+    </row>
+    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="46" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="46" t="s">
+      <c r="B65" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="B65" s="46" t="s">
+    </row>
+    <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="34" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="34" t="s">
+      <c r="B66" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B66" s="34" t="s">
+    </row>
+    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="46" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="46" t="s">
+      <c r="B67" s="46"/>
+    </row>
+    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="B67" s="46"/>
-    </row>
-    <row r="68" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="34" t="s">
+      <c r="B68" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="34" t="s">
+    </row>
+    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="46" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="46" t="s">
+      <c r="B69" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="B69" s="46" t="s">
+    </row>
+    <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="34" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="34" t="s">
+      <c r="B70" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="B70" s="34" t="s">
+      <c r="M70" s="2"/>
+    </row>
+    <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="M70" s="2"/>
-    </row>
-    <row r="71" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="46" t="s">
+      <c r="B71" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="46" t="s">
+      <c r="M71" s="2"/>
+    </row>
+    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="M71" s="2"/>
-    </row>
-    <row r="72" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="34" t="s">
+      <c r="B72" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="B72" s="34" t="s">
+      <c r="M72" s="2"/>
+    </row>
+    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="M72" s="2"/>
-    </row>
-    <row r="73" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="46" t="s">
+      <c r="B73" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="B73" s="46" t="s">
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="34" t="s">
         <v>111</v>
-      </c>
-      <c r="M73" s="2"/>
-    </row>
-    <row r="74" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="34" t="s">
-        <v>112</v>
       </c>
       <c r="B74" s="34"/>
       <c r="M74" s="2"/>
     </row>
-    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="B75" s="46" t="s">
+      <c r="M75" s="2"/>
+    </row>
+    <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="M75" s="2"/>
-    </row>
-    <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="50" t="s">
+      <c r="B76" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="B76" s="34" t="s">
+      <c r="M76" s="2"/>
+    </row>
+    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="M76" s="2"/>
-    </row>
-    <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="49" t="s">
+      <c r="B77" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B77" s="46" t="s">
+      <c r="M77" s="2"/>
+    </row>
+    <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="M77" s="2"/>
-    </row>
-    <row r="78" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="50" t="s">
+      <c r="B78" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="B78" s="34" t="s">
+      <c r="M78" s="2"/>
+    </row>
+    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="M78" s="2"/>
-    </row>
-    <row r="79" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="46" t="s">
+      <c r="B79" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="46" t="s">
-        <v>122</v>
-      </c>
       <c r="M79" s="2"/>
     </row>
-    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="34"/>
       <c r="B80" s="34"/>
       <c r="M80" s="2"/>
     </row>
-    <row r="81" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B81" s="61"/>
       <c r="C81" s="32"/>
       <c r="M81" s="2"/>
     </row>
-    <row r="82" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="34"/>
       <c r="B82" s="34"/>
       <c r="M82" s="2"/>
     </row>
-    <row r="83" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="46"/>
       <c r="B83" s="46"/>
       <c r="M83" s="2"/>
     </row>
-    <row r="84" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="34"/>
       <c r="B84" s="34"/>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="46"/>
       <c r="B85" s="46"/>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="34"/>
       <c r="B86" s="34"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="46"/>
       <c r="B87" s="46"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="51"/>
       <c r="B88" s="52"/>
       <c r="C88" s="28"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="53"/>
       <c r="B89" s="54"/>
       <c r="C89" s="28"/>
       <c r="M89" s="2"/>
     </row>
-    <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="55"/>
       <c r="B90" s="52"/>
       <c r="C90" s="28"/>
       <c r="M90" s="2"/>
     </row>
-    <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="56"/>
       <c r="B91" s="54"/>
       <c r="C91" s="28"/>
     </row>
-    <row r="92" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="55"/>
       <c r="B92" s="52"/>
       <c r="C92" s="28"/>
     </row>
-    <row r="93" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="56"/>
       <c r="B93" s="54"/>
       <c r="C93" s="28"/>
     </row>
-    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="55"/>
       <c r="B94" s="52"/>
       <c r="C94" s="28"/>
     </row>
-    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="56"/>
       <c r="B95" s="54"/>
       <c r="C95" s="28"/>
       <c r="H95" s="3"/>
     </row>
-    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="55"/>
       <c r="B96" s="52"/>
       <c r="C96" s="28"/>
       <c r="H96" s="3"/>
     </row>
-    <row r="97" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="56"/>
       <c r="B97" s="54"/>
       <c r="C97" s="28"/>
@@ -2058,7 +2055,7 @@
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="34"/>
       <c r="B98" s="34"/>
       <c r="G98" s="4"/>
@@ -2066,7 +2063,7 @@
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
     </row>
-    <row r="99" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="45"/>
       <c r="B99" s="54"/>
       <c r="C99" s="33"/>
@@ -2075,7 +2072,7 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="57"/>
       <c r="B100" s="52"/>
       <c r="C100" s="33"/>
@@ -2084,7 +2081,7 @@
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
     </row>
-    <row r="101" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="46"/>
       <c r="B101" s="54"/>
       <c r="C101" s="33"/>
@@ -2093,7 +2090,7 @@
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="34"/>
       <c r="B102" s="52"/>
       <c r="C102" s="33"/>
@@ -2102,7 +2099,7 @@
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
     </row>
-    <row r="103" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="46"/>
       <c r="B103" s="54"/>
       <c r="C103" s="33"/>
@@ -2111,7 +2108,7 @@
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
     </row>
-    <row r="104" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="34"/>
       <c r="B104" s="52"/>
       <c r="C104" s="33"/>
@@ -2120,7 +2117,7 @@
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
     </row>
-    <row r="105" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="46"/>
       <c r="B105" s="54"/>
       <c r="C105" s="33"/>
@@ -2129,7 +2126,7 @@
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
     </row>
-    <row r="106" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="34"/>
       <c r="B106" s="52"/>
       <c r="C106" s="33"/>
@@ -2138,7 +2135,7 @@
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
     </row>
-    <row r="107" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="46"/>
       <c r="B107" s="54"/>
       <c r="C107" s="33"/>
@@ -2147,7 +2144,7 @@
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
     </row>
-    <row r="108" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="34"/>
       <c r="B108" s="52"/>
       <c r="C108" s="33"/>
@@ -2156,7 +2153,7 @@
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
     </row>
-    <row r="109" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="46"/>
       <c r="B109" s="46"/>
       <c r="G109" s="4"/>
@@ -2164,7 +2161,7 @@
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
     </row>
-    <row r="110" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="34"/>
       <c r="B110" s="34"/>
       <c r="G110" s="4"/>
@@ -2172,361 +2169,361 @@
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
     </row>
-    <row r="111" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G111" s="4"/>
       <c r="H111" s="7"/>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
     </row>
-    <row r="112" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G112" s="4"/>
       <c r="H112" s="7"/>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
     </row>
-    <row r="113" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G113" s="4"/>
       <c r="H113" s="7"/>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
     </row>
-    <row r="114" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G114" s="4"/>
       <c r="H114" s="7"/>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
     </row>
-    <row r="115" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G115" s="8"/>
       <c r="H115" s="7"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G116" s="8"/>
       <c r="H116" s="7"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
     </row>
-    <row r="117" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G117" s="8"/>
       <c r="H117" s="7"/>
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
     </row>
-    <row r="118" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G118" s="8"/>
       <c r="H118" s="7"/>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
     </row>
-    <row r="119" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G119" s="8"/>
       <c r="H119" s="7"/>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G120" s="8"/>
       <c r="H120" s="7"/>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G121" s="8"/>
       <c r="H121" s="7"/>
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G122" s="8"/>
       <c r="H122" s="7"/>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
     </row>
-    <row r="123" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G123" s="6"/>
       <c r="H123" s="7"/>
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G124" s="6"/>
       <c r="H124" s="7"/>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
     </row>
-    <row r="125" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G125" s="6"/>
       <c r="H125" s="7"/>
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G126" s="6"/>
       <c r="H126" s="7"/>
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
     </row>
-    <row r="127" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G128" s="6"/>
       <c r="H128" s="7"/>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
     </row>
-    <row r="129" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G129" s="4"/>
       <c r="H129" s="7"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G130" s="4"/>
       <c r="H130" s="7"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
     </row>
-    <row r="131" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G131" s="4"/>
       <c r="H131" s="7"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="7:10" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G132" s="4"/>
       <c r="H132" s="7"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="9"/>
       <c r="B179" s="10"/>
       <c r="C179" s="10"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="9"/>
       <c r="B180" s="10"/>
       <c r="C180" s="10"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="9"/>
       <c r="B181" s="10"/>
       <c r="C181" s="10"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="9"/>
       <c r="B182" s="10"/>
       <c r="C182" s="10"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="9"/>
       <c r="B183" s="10"/>
       <c r="C183" s="10"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="9"/>
       <c r="B184" s="10"/>
       <c r="C184" s="10"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="9"/>
       <c r="B185" s="10"/>
       <c r="C185" s="10"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="9"/>
       <c r="B186" s="10"/>
       <c r="C186" s="10"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="9"/>
       <c r="B187" s="10"/>
       <c r="C187" s="10"/>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="9"/>
       <c r="B188" s="10"/>
       <c r="C188" s="10"/>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="9"/>
       <c r="B189" s="10"/>
       <c r="C189" s="10"/>
     </row>
-    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="9"/>
       <c r="B190" s="11"/>
       <c r="C190" s="10"/>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="9"/>
       <c r="B191" s="10"/>
       <c r="C191" s="10"/>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="13"/>
       <c r="B194" s="10"/>
       <c r="C194" s="10"/>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="13"/>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="12"/>
       <c r="B196" s="16"/>
       <c r="C196" s="16"/>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="12"/>
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="13"/>
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="18"/>
       <c r="B199" s="10"/>
       <c r="C199" s="10"/>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="18"/>
       <c r="B200" s="19"/>
       <c r="C200" s="20"/>
       <c r="D200" s="10"/>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="18"/>
       <c r="B201" s="10"/>
       <c r="C201" s="20"/>
       <c r="D201" s="10"/>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="13"/>
       <c r="B202" s="21"/>
       <c r="C202" s="10"/>
       <c r="D202" s="10"/>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="13"/>
       <c r="B203" s="22"/>
       <c r="C203" s="10"/>
       <c r="D203" s="10"/>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="13"/>
       <c r="B204" s="21"/>
       <c r="C204" s="23"/>
       <c r="D204" s="10"/>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="12"/>
       <c r="B205" s="10"/>
       <c r="C205" s="24"/>
       <c r="D205" s="10"/>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="25"/>
       <c r="B206" s="25"/>
       <c r="C206" s="25"/>
       <c r="D206" s="12"/>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D207" s="10"/>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D208" s="10"/>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D209" s="10"/>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D210" s="10"/>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D211" s="10"/>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D212" s="10"/>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D213" s="10"/>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D214" s="10"/>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D215" s="10"/>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D216" s="10"/>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="26"/>
       <c r="B217" s="27"/>
       <c r="C217" s="28"/>
       <c r="D217" s="10"/>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="12"/>
       <c r="D218" s="12"/>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D219" s="10"/>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D220" s="10"/>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D221" s="10"/>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D222" s="10"/>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D223" s="10"/>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D224" s="10"/>
     </row>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="225" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D225" s="10"/>
     </row>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="226" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D226" s="10"/>
     </row>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="227" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D227" s="10"/>
     </row>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="228" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D228" s="10"/>
     </row>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="229" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D229" s="10"/>
     </row>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.15">
+    <row r="230" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D230" s="10"/>
     </row>
   </sheetData>
